--- a/maintenance/PreformFeedAssembly_Maintenance_Tracker_Template.xlsx
+++ b/maintenance/PreformFeedAssembly_Maintenance_Tracker_Template.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:X7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,26 @@
           <t>Last Done Furnace Hours</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Required Parts</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Planning months</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Estimated duration min</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -613,6 +633,22 @@
       <c r="T2" t="n">
         <v>0</v>
       </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>IPA wipes / cleaning cloth</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="X2" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -697,6 +733,22 @@
       <c r="T3" t="n">
         <v>0</v>
       </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Light machine oil</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>3-Month</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X3" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -781,6 +833,22 @@
       <c r="T4" t="n">
         <v>0</v>
       </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Light machine oil</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>3-Month</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -865,6 +933,22 @@
       <c r="T5" t="n">
         <v>0</v>
       </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Grease (NLGI-2)</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>3-Month</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>3</v>
+      </c>
+      <c r="X5" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -949,6 +1033,22 @@
       <c r="T6" t="n">
         <v>0</v>
       </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Grease (NLGI-2)</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>3-Month</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>3</v>
+      </c>
+      <c r="X6" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1032,6 +1132,22 @@
       </c>
       <c r="T7" t="n">
         <v>0</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Light machine oil</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>3-Month</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>3</v>
+      </c>
+      <c r="X7" t="n">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/maintenance/PreformFeedAssembly_Maintenance_Tracker_Template.xlsx
+++ b/maintenance/PreformFeedAssembly_Maintenance_Tracker_Template.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X7"/>
+  <dimension ref="A1:AB7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,26 @@
           <t>Estimated duration min</t>
         </is>
       </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Last_Done_Draw</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Last_Done_Hours_UV1</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Last_Done_Hours_UV2</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Last_Done_Hours_Furnace</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -589,7 +609,6 @@
           <t>calendar</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>days</t>
@@ -621,14 +640,10 @@
           <t>Failure to maintain cleanliness and smooth operation can lead to clamp malfunction and potential preform damage.</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
+          <t>2026-04-04</t>
+        </is>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -689,7 +704,6 @@
           <t>calendar</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>months</t>
@@ -721,14 +735,10 @@
           <t>Apply sparingly; remove excess oil to avoid contamination.</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
-        </is>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
+          <t>2026-02-04</t>
+        </is>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -789,7 +799,6 @@
           <t>calendar</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>months</t>
@@ -821,14 +830,10 @@
           <t>Avoid over-lubrication; wipe away excess oil.</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
+          <t>2026-02-04</t>
+        </is>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -889,7 +894,6 @@
           <t>calendar</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>months</t>
@@ -921,14 +925,10 @@
           <t>Do not over-grease; ensure even distribution.</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
-        </is>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
+          <t>2026-02-04</t>
+        </is>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -989,7 +989,6 @@
           <t>calendar</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>months</t>
@@ -1021,14 +1020,10 @@
           <t>Inspect ball screw before greasing; remove excess grease.</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
-        </is>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
+          <t>2026-02-04</t>
+        </is>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1089,7 +1084,6 @@
           <t>calendar</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>months</t>
@@ -1121,14 +1115,10 @@
           <t>Light oil only; cleanliness is critical.</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
-        </is>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
+          <t>2026-02-04</t>
+        </is>
       </c>
       <c r="T7" t="n">
         <v>0</v>
